--- a/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -1341,13 +1341,16 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>Detailed dosage instructions</t>
+  </si>
+  <si>
+    <t>Provides detailed dosage instructions in the same way that they are described for MedicationRequest resources.</t>
   </si>
   <si>
     <t>If a dosage instruction is used, the definition should not specify timing or quantity.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM; moodCode=DEFN]</t>
   </si>
   <si>
     <t>ActivityDefinition.bodySite</t>
@@ -8017,10 +8020,10 @@
         <v>427</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8088,7 +8091,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8099,10 +8102,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8128,16 +8131,16 @@
         <v>252</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8165,10 +8168,10 @@
         <v>300</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8186,7 +8189,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8204,7 +8207,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8215,10 +8218,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8241,17 +8244,17 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8300,7 +8303,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8329,10 +8332,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8355,17 +8358,17 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8414,7 +8417,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8443,10 +8446,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8469,13 +8472,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8526,7 +8529,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8555,10 +8558,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8581,16 +8584,16 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8640,7 +8643,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8669,10 +8672,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8698,13 +8701,13 @@
         <v>383</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8754,7 +8757,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8783,10 +8786,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8895,10 +8898,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9009,10 +9012,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9125,10 +9128,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9154,13 +9157,13 @@
         <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9210,7 +9213,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -9239,10 +9242,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9265,16 +9268,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9324,7 +9327,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -361,7 +361,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -647,7 +647,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)canonical</t>
+Reference(Group|4.3.0)canonical</t>
   </si>
   <si>
     <t>Type of individual the activity definition is intended for</t>
@@ -668,7 +668,7 @@
     <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.3.0</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -815,7 +815,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.3.0</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -953,7 +953,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.3.0</t>
   </si>
   <si>
     <t>ActivityDefinition.author</t>
@@ -1026,7 +1026,7 @@
     <t>ActivityDefinition.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.3.0)
 </t>
   </si>
   <si>
@@ -1063,7 +1063,7 @@
     <t>ActivityDefinition.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -1097,7 +1097,7 @@
     <t>Detailed type of the activity; e.g. CBC.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.3.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -1180,7 +1180,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.3.0)
 </t>
   </si>
   <si>
@@ -1321,7 +1321,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.3.0}
 </t>
   </si>
   <si>
@@ -1371,7 +1371,7 @@
     <t>A code that identifies the anatomical location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
   </si>
   <si>
     <t>.targetSiteCode {for classCode=PROC, SBADM}</t>
@@ -1380,7 +1380,7 @@
     <t>ActivityDefinition.specimenRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(SpecimenDefinition)
+    <t xml:space="preserve">Reference(SpecimenDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -1396,7 +1396,7 @@
     <t>ActivityDefinition.observationRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ObservationDefinition)
+    <t xml:space="preserve">Reference(ObservationDefinition|4.3.0)
 </t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>ActivityDefinition.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.3.0)
 </t>
   </si>
   <si>
@@ -1787,17 +1787,17 @@
   <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.60546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.60546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.81640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.81640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="69.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1806,26 +1806,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="93.40625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="80.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.82421875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.34765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="56.328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="133.84765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.2890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="114.75" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-activitydefinition-chemotherapyregimen-oral.xlsx
@@ -265,8 +265,8 @@
     <t>TBD</t>
   </si>
   <si>
-    <t>cnl-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.exists() implies name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
-dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>cnl-0:名称は、コード生成などの機械処理アプリケーションによるモジュールの識別子として使用できるべきである / Name should be usable as an identifier for the module by machine processing applications such as code generation {name.exists() implies name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}
+dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Act[classCode=ACT; moodCode=DEFN]</t>
@@ -288,13 +288,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -307,16 +307,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -327,13 +327,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -346,19 +346,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -378,13 +378,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -404,19 +404,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -434,33 +434,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ActivityDefinition.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -469,18 +470,20 @@
     <t>ActivityDefinition.url</t>
   </si>
   <si>
-    <t>Canonical identifier for this activity definition, represented as a URI (globally unique)</t>
-  </si>
-  <si>
-    <t>An absolute URI that is used to identify this activity definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this activity definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the activity definition is stored on different servers.</t>
-  </si>
-  <si>
-    <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
+    <t>このアクティビティ定義の標準identifier、URI（グローバルに一意）として表される / Canonical identifier for this activity definition, represented as a URI (globally unique)</t>
+  </si>
+  <si>
+    <t>このアクティビティ定義を識別するために使用される絶対URIは、仕様、モデル、設計、またはインスタンスで参照されている場合に使用されます。その標準identifierとも呼ばれます。これはグローバルにユニークである必要があり、このアクティビティ定義の権威あるインスタンスが公開される（または公開される）文字通りのアドレスである必要があります。このURLは、標準的な参照のターゲットになる可能性があります。アクティビティ定義が異なるサーバーに保存されている場合、同じままになります。 / An absolute URI that is used to identify this activity definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this activity definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the activity definition is stored on different servers.</t>
+  </si>
+  <si>
+    <t>urn：uuid：またはurn：oid：しかし、実際のhttp：アドレスが望ましいです。複数のインスタンスが異なるバージョンがある場合、同じURLを共有する場合があります。
+新しいバージョンのリソース（同じURL、新しいバージョン）を作成するタイミングの決定と新しいアーティファクトの定義は、著者次第です。この決定を行うための考慮事項は、[テクニカルバージョンとビジネスバージョン]（resource.html＃バージョン）にあります。
+場合によっては、リソースは記載されているURLで見つけることができなくなりますが、URL自体は変更できません。実装では、[Meta.Source]（Resource.html＃Meta）要素を使用して、リソースの現在のマスターソースがどこにあるかを示すことができます。 / Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
 The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4B/resource.html#versions). 
 In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4B/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
   </si>
   <si>
-    <t>Allows the activity definition to be referenced by a single globally unique identifier.</t>
+    <t>アクティビティ定義を単一のグローバルに一意のidentifierによって参照できるようにします。 / Allows the activity definition to be referenced by a single globally unique identifier.</t>
   </si>
   <si>
     <t>Definition.url</t>
@@ -499,16 +502,16 @@
 </t>
   </si>
   <si>
-    <t>Additional identifier for the activity definition</t>
-  </si>
-  <si>
-    <t>A formal identifier that is used to identify this activity definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
-  </si>
-  <si>
-    <t>Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this activity definition outside of FHIR, where it is not possible to use the logical URI.</t>
-  </si>
-  <si>
-    <t>Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
+    <t>アクティビティ定義の追加identifier / Additional identifier for the activity definition</t>
+  </si>
+  <si>
+    <t>このアクティビティ定義を他の形式で表現した場合、または仕様、モデル、設計、またはインスタンスで参照される場合に使用される正式なidentifier。 / A formal identifier that is used to identify this activity definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
+  </si>
+  <si>
+    <t>通常、これは、HL7 V3 II（インスタンスidentifier）データ型に移動できるidentifierに使用され、論理URIを使用できないFHIR以外でこのアクティビティ定義を識別できます。 / Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this activity definition outside of FHIR, where it is not possible to use the logical URI.</t>
+  </si>
+  <si>
+    <t>外部から提供可能なビジネスidentifierをモジュールに簡単に関連付けることができます。 / Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
   </si>
   <si>
     <t>Definition.identifier</t>
@@ -527,13 +530,13 @@
 </t>
   </si>
   <si>
-    <t>Business version of the activity definition</t>
-  </si>
-  <si>
-    <t>The identifier that is used to identify this version of the activity definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the activity definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active assets.</t>
-  </si>
-  <si>
-    <t>There may be different activity definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the activity definition with the format [url]|[version].</t>
+    <t>アクティビティ定義のビジネスバージョン / Business version of the activity definition</t>
+  </si>
+  <si>
+    <t>このバージョンのアクティビティ定義を識別するために使用されるidentifierは、仕様、モデル、デザイン、またはインスタンスで参照されている場合です。これは、アクティビティ定義著者によって管理される任意の価値であり、グローバルにユニークであるとは期待されていません。たとえば、マネージドバージョンが利用できない場合は、タイムスタンプ（Yyyymmddなど）かもしれません。また、バージョンを辞書的なシーケンスに配置できるという期待もありません。意思決定サポートサービスの仕様と一致するバージョンを提供するには、Major.minor.revisionの形式（1.0.0など）を使用します。バージョンの知識資産の詳細については、意思決定支援サービスの仕様を参照してください。非実験的アクティブアセットにはバージョンが必要であることに注意してください。 / The identifier that is used to identify this version of the activity definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the activity definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active assets.</t>
+  </si>
+  <si>
+    <t>同じidentifierを持っているが異なるバージョンを持つさまざまなアクティビティ定義インスタンスがある場合があります。バージョンは、[url] | [バージョン]を使用して、アクティビティ定義の特定のビジネスバージョンへの参照を許可するために、参照にURLに追加できます。 / There may be different activity definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the activity definition with the format [url]|[version].</t>
   </si>
   <si>
     <t>Definition.version</t>
@@ -548,16 +551,16 @@
     <t>ActivityDefinition.name</t>
   </si>
   <si>
-    <t>Name for this activity definition (computer friendly)</t>
-  </si>
-  <si>
-    <t>A natural language name identifying the activity definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
-  </si>
-  <si>
-    <t>The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
-  </si>
-  <si>
-    <t>Support human navigation and code generation.</t>
+    <t>このアクティビティ定義の名前（コンピューターフレンドリー） / Name for this activity definition (computer friendly)</t>
+  </si>
+  <si>
+    <t>アクティビティ定義を識別する自然言語名。この名前は、コード生成などのマシン処理アプリケーションにより、モジュールのidentifierとして使用できる必要があります。 / A natural language name identifying the activity definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
+  </si>
+  <si>
+    <t>名前はグローバルにユニークであるとは予想されていません。名前は、機械加工に優しいことを確認するための単純な英数字タイプの名前である必要があります。 / The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
+  </si>
+  <si>
+    <t>ヒューマンナビゲーションとコード生成をサポートします。 / Support human navigation and code generation.</t>
   </si>
   <si>
     <t xml:space="preserve">cnl-0
@@ -567,13 +570,13 @@
     <t>ActivityDefinition.title</t>
   </si>
   <si>
-    <t>Name for this activity definition (human friendly)</t>
-  </si>
-  <si>
-    <t>A short, descriptive, user-friendly title for the activity definition.</t>
-  </si>
-  <si>
-    <t>This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
+    <t>このアクティビティ定義の名前（人間に優しい） / Name for this activity definition (human friendly)</t>
+  </si>
+  <si>
+    <t>アクティビティ定義の短い、説明的でユーザーフレンドリーなタイトル。 / A short, descriptive, user-friendly title for the activity definition.</t>
+  </si>
+  <si>
+    <t>この名前は、機械加工に優しいものである必要はなく、句読点、ホワイトスペースなどが含まれている場合があります。 / This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
   </si>
   <si>
     <t>Definition.title</t>
@@ -585,28 +588,28 @@
     <t>ActivityDefinition.subtitle</t>
   </si>
   <si>
-    <t>Subordinate title of the activity definition</t>
-  </si>
-  <si>
-    <t>An explanatory or alternate title for the activity definition giving additional information about its content.</t>
+    <t>アクティビティ定義の下位タイトル / Subordinate title of the activity definition</t>
+  </si>
+  <si>
+    <t>コンテンツに関する追加情報を提供するアクティビティ定義の説明または代替タイトル。 / An explanatory or alternate title for the activity definition giving additional information about its content.</t>
   </si>
   <si>
     <t>ActivityDefinition.status</t>
   </si>
   <si>
-    <t>draft | active | retired | unknown</t>
-  </si>
-  <si>
-    <t>The status of this activity definition. Enables tracking the life-cycle of the content.</t>
-  </si>
-  <si>
-    <t>Allows filtering of activity definitions that are appropriate for use versus not.</t>
+    <t>ドラフト|アクティブ|引退|わからない / draft | active | retired | unknown</t>
+  </si>
+  <si>
+    <t>このアクティビティ定義のステータス。コンテンツのライフサイクルを追跡することができます。 / The status of this activity definition. Enables tracking the life-cycle of the content.</t>
+  </si>
+  <si>
+    <t>使用に適したアクティビティ定義のフィルタリングを使用できます。 / Allows filtering of activity definitions that are appropriate for use versus not.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The lifecycle status of an artifact.</t>
+    <t>アーティファクトのライフサイクルステータス。 / The lifecycle status of an artifact.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/publication-status|4.3.0</t>
@@ -628,13 +631,13 @@
 </t>
   </si>
   <si>
-    <t>For testing purposes, not real usage</t>
-  </si>
-  <si>
-    <t>A Boolean value to indicate that this activity definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
-  </si>
-  <si>
-    <t>Enables experimental content to be developed following the same lifecycle that would be used for a production-level activity definition.</t>
+    <t>テスト目的で、実際の使用法ではありません / For testing purposes, not real usage</t>
+  </si>
+  <si>
+    <t>このアクティビティ定義は、テスト目的（または教育/評価/マーケティング）のために執筆されており、本物の使用に使用されることを意図していないことを示すブール値。 / A Boolean value to indicate that this activity definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
+  </si>
+  <si>
+    <t>生産レベルのアクティビティ定義に使用される同じライフサイクルに従って、実験コンテンツを開発できるようにします。 / Enables experimental content to be developed following the same lifecycle that would be used for a production-level activity definition.</t>
   </si>
   <si>
     <t>Definition.experimental</t>
@@ -650,22 +653,22 @@
 Reference(Group|4.3.0)canonical</t>
   </si>
   <si>
-    <t>Type of individual the activity definition is intended for</t>
-  </si>
-  <si>
-    <t>A code, group definition, or canonical reference that describes  or identifies the intended subject of the activity being defined.  Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
-  </si>
-  <si>
-    <t>Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
-  </si>
-  <si>
-    <t>Patient</t>
+    <t>個別のタイプアクティビティ定義は目的です / Type of individual the activity definition is intended for</t>
+  </si>
+  <si>
+    <t>定義されている活動の対象となる主題を記述または識別するコード、グループ定義、またはカノニカル参照。カノニカル参照は、医薬品および物質の品質仕様のプロトコル定義をサポートするために許可されており、MedicinalProductDefinition、SubstanceDefinition、AdministrableProductDefinition、ManufacturedItemDefinition、またはPackagedProductDefinitionリソースを参照できます。 / A code, group definition, or canonical reference that describes  or identifies the intended subject of the activity being defined.  Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
+  </si>
+  <si>
+    <t>subject要素のcanonical型の選択肢はR4Bで医薬品品質のユースケースをサポートするために導入されたことに注意。できるだけ後方互換性を確保するため、新しいcanonical型はこれらのユースケースでのみ使用することが推奨される。 / Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
+  </si>
+  <si>
+    <t>忍耐強い / Patient</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
+    <t>活動の可能性のある被験者（患者、開業医、組織、場所など）の可能性のあるタイプ。 / The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/subject-type|4.3.0</t>
@@ -688,13 +691,13 @@
 </t>
   </si>
   <si>
-    <t>Date last changed</t>
-  </si>
-  <si>
-    <t>The date  (and optionally time) when the activity definition was published. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the activity definition changes.</t>
-  </si>
-  <si>
-    <t>Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the activity definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
+    <t>日付は最後に変更されました / Date last changed</t>
+  </si>
+  <si>
+    <t>アクティビティ定義が公開された日付（およびオプションで時間）。ビジネスバージョンが変更されたときに日付が変更され、ステータスコードが変更された場合は変更する必要があります。さらに、アクティビティ定義の実質的な内容が変更されると、変更する必要があります。 / The date  (and optionally time) when the activity definition was published. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the activity definition changes.</t>
+  </si>
+  <si>
+    <t>リソースはアクティビティ定義の二次表現である可能性があるため、これはリソースラスト修飾日と同じではないことに注意してください。追加の特定の日付は、拡張機能として追加されるか、リソースの過去のバージョンに関連する提案に相談することで見つけることができます。 / Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the activity definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
   </si>
   <si>
     <t>Definition.date</t>
@@ -709,16 +712,16 @@
     <t>ActivityDefinition.publisher</t>
   </si>
   <si>
-    <t>Name of the publisher (organization or individual)</t>
-  </si>
-  <si>
-    <t>The name of the organization or individual that published the activity definition.</t>
-  </si>
-  <si>
-    <t>Usually an organization but may be an individual. The publisher (or steward) of the activity definition is the organization or individual primarily responsible for the maintenance and upkeep of the activity definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the activity definition. This item SHOULD be populated unless the information is available from context.</t>
-  </si>
-  <si>
-    <t>Helps establish the "authority/credibility" of the activity definition.  May also allow for contact.</t>
+    <t>出版社の名前（組織または個人） / Name of the publisher (organization or individual)</t>
+  </si>
+  <si>
+    <t>アクティビティ定義を公開した組織または個人の名前。 / The name of the organization or individual that published the activity definition.</t>
+  </si>
+  <si>
+    <t>通常、組織ですが、個人かもしれません。アクティビティ定義のパブリッシャー（またはスチュワード）は、アクティビティ定義のメンテナンスと維持の主な責任を負う組織または個人です。これは、必ずしもコンテンツを開発し、最初に執筆した個人または組織ではありません。出版社は、アクティビティ定義に関する質問または問題の連絡先の主要なポイントです。情報がコンテキストから利用可能でない限り、このアイテムは入力する必要があります。 / Usually an organization but may be an individual. The publisher (or steward) of the activity definition is the organization or individual primarily responsible for the maintenance and upkeep of the activity definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the activity definition. This item SHOULD be populated unless the information is available from context.</t>
+  </si>
+  <si>
+    <t>アクティビティ定義の「権限/信頼性」を確立するのに役立ちます。また、接触を許可する場合があります。 / Helps establish the "authority/credibility" of the activity definition.  May also allow for contact.</t>
   </si>
   <si>
     <t>Definition.publisher {as string instead of CodeableConcept}</t>
@@ -737,13 +740,13 @@
 </t>
   </si>
   <si>
-    <t>Contact details for the publisher</t>
-  </si>
-  <si>
-    <t>Contact details to assist a user in finding and communicating with the publisher.</t>
-  </si>
-  <si>
-    <t>May be a web site, an email address, a telephone number, etc.</t>
+    <t>出版社の連絡先の詳細 / Contact details for the publisher</t>
+  </si>
+  <si>
+    <t>ユーザーがパブリッシャーを見つけて通信するのを支援する連絡先の詳細。 / Contact details to assist a user in finding and communicating with the publisher.</t>
+  </si>
+  <si>
+    <t>Webサイト、電子メールアドレス、電話番号などです。 / May be a web site, an email address, a telephone number, etc.</t>
   </si>
   <si>
     <t>Definition.contact</t>
@@ -759,13 +762,13 @@
 </t>
   </si>
   <si>
-    <t>Natural language description of the activity definition</t>
-  </si>
-  <si>
-    <t>A free text natural language description of the activity definition from a consumer's perspective.</t>
-  </si>
-  <si>
-    <t>This description can be used to capture details such as why the activity definition was built, comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the activity definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the activity definition is presumed to be the predominant language in the place the activity definition was created).</t>
+    <t>アクティビティ定義の自然言語説明 / Natural language description of the activity definition</t>
+  </si>
+  <si>
+    <t>消費者の観点からのアクティビティ定義の無料テキスト自然言語説明。 / A free text natural language description of the activity definition from a consumer's perspective.</t>
+  </si>
+  <si>
+    <t>この説明は、アクティビティ定義が作成された理由、誤用に関するコメント、臨床使用と解釈の指示、文献の参照、紙の世界からの例などの詳細をキャプチャするために使用できます。伝達されるアクティビティ定義のレンダリングではありません。リソース自体の「テキスト」フィールド。この項目は、情報がコンテキストから利用可能でない限り入力する必要があります（たとえば、アクティビティ定義の言語は、アクティビティ定義が作成された場所の主要な言語であると推定されます）。 / This description can be used to capture details such as why the activity definition was built, comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the activity definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the activity definition is presumed to be the predominant language in the place the activity definition was created).</t>
   </si>
   <si>
     <t>Definition.description</t>
@@ -781,16 +784,16 @@
 </t>
   </si>
   <si>
-    <t>The context that the content is intended to support</t>
-  </si>
-  <si>
-    <t>The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate activity definition instances.</t>
-  </si>
-  <si>
-    <t>When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
-  </si>
-  <si>
-    <t>Assist in searching for appropriate content.</t>
+    <t>コンテンツがサポートすることを意図しているというコンテキスト / The context that the content is intended to support</t>
+  </si>
+  <si>
+    <t>コンテンツは、リストされているコンテキストをサポートすることを目的として開発されました。これらのコンテキストは、一般的なカテゴリ（性別、年齢、...）であるか、特定のプログラム（保険プラン、研究など）への参照である場合があり、適切なアクティビティ定義インスタンスのインデックス作成と検索を支援するために使用できます。 / The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate activity definition instances.</t>
+  </si>
+  <si>
+    <t>複数のUSECONTEXTSが指定されている場合、すべてまたはどのコンテキストが適用されるという期待はありません。 / When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
+  </si>
+  <si>
+    <t>適切なコンテンツの検索を支援します。 / Assist in searching for appropriate content.</t>
   </si>
   <si>
     <t>Definition.useContext</t>
@@ -803,16 +806,16 @@
 </t>
   </si>
   <si>
-    <t>Intended jurisdiction for activity definition (if applicable)</t>
-  </si>
-  <si>
-    <t>A legal or geographic region in which the activity definition is intended to be used.</t>
-  </si>
-  <si>
-    <t>It may be possible for the activity definition to be used in jurisdictions other than those for which it was originally designed or intended.</t>
-  </si>
-  <si>
-    <t>Countries and regions within which this artifact is targeted for use.</t>
+    <t>アクティビティ定義のための対象管轄区域（該当する場合） / Intended jurisdiction for activity definition (if applicable)</t>
+  </si>
+  <si>
+    <t>アクティビティ定義が使用されることを目的としている法的または地理的地域。 / A legal or geographic region in which the activity definition is intended to be used.</t>
+  </si>
+  <si>
+    <t>アクティビティ定義は、元々設計または意図されたもの以外の管轄区域で使用される可能性があります。 / It may be possible for the activity definition to be used in jurisdictions other than those for which it was originally designed or intended.</t>
+  </si>
+  <si>
+    <t>このアーティファクトが使用することを目的としている国と地域。 / Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.3.0</t>
@@ -824,13 +827,13 @@
     <t>ActivityDefinition.purpose</t>
   </si>
   <si>
-    <t>Why this activity definition is defined</t>
-  </si>
-  <si>
-    <t>Explanation of why this activity definition is needed and why it has been designed as it has.</t>
-  </si>
-  <si>
-    <t>This element does not describe the usage of the activity definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this activity definition.</t>
+    <t>このアクティビティ定義が定義される理由 / Why this activity definition is defined</t>
+  </si>
+  <si>
+    <t>このアクティビティ定義が必要な理由と、それがそのまま設計された理由の説明。 / Explanation of why this activity definition is needed and why it has been designed as it has.</t>
+  </si>
+  <si>
+    <t>この要素は、アクティビティ定義の使用法を説明していません。代わりに、リソースが必要であるか、「なぜ」のどちらかのように定義されている「なぜ」のトレーサビリティを提供します。これは、このアクティビティ定義の構造を促進する材料または仕様を調達するために使用できます。 / This element does not describe the usage of the activity definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this activity definition.</t>
   </si>
   <si>
     <t>Definition.purpose</t>
@@ -845,10 +848,10 @@
     <t>ActivityDefinition.usage</t>
   </si>
   <si>
-    <t>Describes the clinical usage of the activity definition</t>
-  </si>
-  <si>
-    <t>A detailed description of how the activity definition is used from a clinical perspective.</t>
+    <t>活動定義の臨床的使用について説明します / Describes the clinical usage of the activity definition</t>
+  </si>
+  <si>
+    <t>臨床的観点から活動定義がどのように使用されるかの詳細な説明。 / A detailed description of how the activity definition is used from a clinical perspective.</t>
   </si>
   <si>
     <t>ActivityDefinition.copyright</t>
@@ -858,13 +861,13 @@
 Restrictions</t>
   </si>
   <si>
-    <t>Use and/or publishing restrictions</t>
-  </si>
-  <si>
-    <t>A copyright statement relating to the activity definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the activity definition.</t>
-  </si>
-  <si>
-    <t>Consumers must be able to determine any legal restrictions on the use of the activity definition and/or its content.</t>
+    <t>使用および/または公開制限 / Use and/or publishing restrictions</t>
+  </si>
+  <si>
+    <t>アクティビティ定義および/またはその内容に関する著作権ステートメント。著作権声明は、一般に、アクティビティ定義の使用と公開に関する法的制限です。 / A copyright statement relating to the activity definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the activity definition.</t>
+  </si>
+  <si>
+    <t>消費者は、アクティビティ定義および/またはそのコンテンツの使用に関する法的制限を決定できる必要があります。 / Consumers must be able to determine any legal restrictions on the use of the activity definition and/or its content.</t>
   </si>
   <si>
     <t>Definition.copyright</t>
@@ -877,13 +880,13 @@
 </t>
   </si>
   <si>
-    <t>When the activity definition was approved by publisher</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
-  </si>
-  <si>
-    <t>The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.</t>
+    <t>アクティビティ定義が出版社によって承認されたとき / When the activity definition was approved by publisher</t>
+  </si>
+  <si>
+    <t>リソースコンテンツが出版社によって承認された日付。承認は、コンテンツの使用が正式に承認されたときに1回発生します。 / The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
+  </si>
+  <si>
+    <t>「日付」要素は、軽度の変更または編集の修正のため、承認日よりも最近のものです。 / The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.</t>
   </si>
   <si>
     <t>Definition.approvalDate</t>
@@ -895,16 +898,16 @@
     <t>ActivityDefinition.lastReviewDate</t>
   </si>
   <si>
-    <t>When the activity definition was last reviewed</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
-  </si>
-  <si>
-    <t>If specified, this date follows the original approval date.</t>
-  </si>
-  <si>
-    <t>Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
+    <t>アクティビティ定義が最後にレビューされたとき / When the activity definition was last reviewed</t>
+  </si>
+  <si>
+    <t>リソースコンテンツが最後にレビューされた日付。レビューは承認後に定期的に行われますが、元の承認日は変更されません。 / The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
+  </si>
+  <si>
+    <t>指定されている場合、この日付は元の承認日に従います。 / If specified, this date follows the original approval date.</t>
+  </si>
+  <si>
+    <t>コンテンツがどれほど「現在」であるかの感覚を与えます。長い間レビューされていないリソースは、適切/関連性が低くなるリスクがある場合があります。 / Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
   </si>
   <si>
     <t>Definition.lastReviewDate</t>
@@ -920,16 +923,16 @@
 </t>
   </si>
   <si>
-    <t>When the activity definition is expected to be used</t>
-  </si>
-  <si>
-    <t>The period during which the activity definition content was or is planned to be in active use.</t>
-  </si>
-  <si>
-    <t>The effective period for a activity definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a measure intended to be used for the year 2016 might be published in 2015.</t>
-  </si>
-  <si>
-    <t>Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the activity definition are or are expected to be used instead.</t>
+    <t>アクティビティ定義が使用されると予想される場合 / When the activity definition is expected to be used</t>
+  </si>
+  <si>
+    <t>アクティビティ定義コンテンツがアクティブに使用されるか、または計画されている期間。 / The period during which the activity definition content was or is planned to be in active use.</t>
+  </si>
+  <si>
+    <t>アクティビティ定義の有効期間は、コンテンツが使用に適用され、公開およびレビューの日付とは独立している時期を決定します。たとえば、2016年に使用することを目的とした尺度は、2015年に公開される場合があります。 / The effective period for a activity definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a measure intended to be used for the year 2016 might be published in 2015.</t>
+  </si>
+  <si>
+    <t>リソースが施行される前に遷移を確立することができ、アクティビティ定義の新しいバージョンが代わりに使用される場合と予想される場合、日没プロセスを許可します。 / Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the activity definition are or are expected to be used instead.</t>
   </si>
   <si>
     <t>Definition.effectivePeriod</t>
@@ -938,19 +941,19 @@
     <t>ActivityDefinition.topic</t>
   </si>
   <si>
-    <t>E.g. Education, Treatment, Assessment, etc.</t>
-  </si>
-  <si>
-    <t>Descriptive topics related to the content of the activity. Topics provide a high-level categorization of the activity that can be useful for filtering and searching.</t>
-  </si>
-  <si>
-    <t>Repositories must be able to determine how to categorize the activity definition so that it can be found by topical searches.</t>
+    <t>例えば。教育、治療、評価など / E.g. Education, Treatment, Assessment, etc.</t>
+  </si>
+  <si>
+    <t>アクティビティの内容に関連する説明的なトピック。トピックは、フィルタリングと検索に役立つアクティビティの高レベルの分類を提供します。 / Descriptive topics related to the content of the activity. Topics provide a high-level categorization of the activity that can be useful for filtering and searching.</t>
+  </si>
+  <si>
+    <t>リポジトリは、アクティビティ定義を分類する方法を決定して、局所検索によって見つけることができる必要があります。 / Repositories must be able to determine how to categorize the activity definition so that it can be found by topical searches.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
+    <t>検索、ソート、フィルタリングに使用される定義の高レベルの分類。 / High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/definition-topic|4.3.0</t>
@@ -959,10 +962,10 @@
     <t>ActivityDefinition.author</t>
   </si>
   <si>
-    <t>Who authored the content</t>
-  </si>
-  <si>
-    <t>An individiual or organization primarily involved in the creation and maintenance of the content.</t>
+    <t>誰がコンテンツを執筆しましたか / Who authored the content</t>
+  </si>
+  <si>
+    <t>主にコンテンツの作成とメンテナンスに関与する個人または組織。 / An individiual or organization primarily involved in the creation and maintenance of the content.</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT]</t>
@@ -971,10 +974,10 @@
     <t>ActivityDefinition.editor</t>
   </si>
   <si>
-    <t>Who edited the content</t>
-  </si>
-  <si>
-    <t>An individual or organization primarily responsible for internal coherence of the content.</t>
+    <t>コンテンツを編集した人 / Who edited the content</t>
+  </si>
+  <si>
+    <t>主にコンテンツの内部一貫性を担当する個人または組織。 / An individual or organization primarily responsible for internal coherence of the content.</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT] { not a great match, but there does not appear to be an editor concept in V3 participation }</t>
@@ -983,10 +986,10 @@
     <t>ActivityDefinition.reviewer</t>
   </si>
   <si>
-    <t>Who reviewed the content</t>
-  </si>
-  <si>
-    <t>An individual or organization primarily responsible for review of some aspect of the content.</t>
+    <t>コンテンツをレビューした人 / Who reviewed the content</t>
+  </si>
+  <si>
+    <t>コンテンツのいくつかの側面のレビューを主に担当する個人または組織。 / An individual or organization primarily responsible for review of some aspect of the content.</t>
   </si>
   <si>
     <t>.participation[typeCode=VRF] {not clear whether VRF best corresponds to reviewer or endorser}</t>
@@ -995,10 +998,10 @@
     <t>ActivityDefinition.endorser</t>
   </si>
   <si>
-    <t>Who endorsed the content</t>
-  </si>
-  <si>
-    <t>An individual or organization responsible for officially endorsing the content for use in some setting.</t>
+    <t>誰がコンテンツを承認しましたか / Who endorsed the content</t>
+  </si>
+  <si>
+    <t>一部の設定で使用するためにコンテンツを公式に支持する個人または組織。 / An individual or organization responsible for officially endorsing the content for use in some setting.</t>
   </si>
   <si>
     <t>ActivityDefinition.relatedArtifact</t>
@@ -1008,16 +1011,16 @@
 </t>
   </si>
   <si>
-    <t>Additional documentation, citations, etc.</t>
-  </si>
-  <si>
-    <t>Related artifacts such as additional documentation, justification, or bibliographic references.</t>
-  </si>
-  <si>
-    <t>Each related artifact is either an attachment, or a reference to another resource, but not both.</t>
-  </si>
-  <si>
-    <t>Activity definitions must be able to provide enough information for consumers of the content (and/or interventions or results produced by the content) to be able to determine and understand the justification for and evidence in support of the content.</t>
+    <t>追加のドキュメント、引用など / Additional documentation, citations, etc.</t>
+  </si>
+  <si>
+    <t>追加のドキュメント、正当化、書誌参照などの関連アーチファクト。 / Related artifacts such as additional documentation, justification, or bibliographic references.</t>
+  </si>
+  <si>
+    <t>関連する各アーティファクトは、添付ファイルまたは別のリソースへの参照のいずれかですが、両方ではありません。 / Each related artifact is either an attachment, or a reference to another resource, but not both.</t>
+  </si>
+  <si>
+    <t>コンテンツを支持する正当性と証拠を決定および理解できるように、アクティビティの定義は、コンテンツの消費者（および/またはコンテンツによって生成された介入または結果）の十分な情報を提供できる必要があります。 / Activity definitions must be able to provide enough information for consumers of the content (and/or interventions or results produced by the content) to be able to determine and understand the justification for and evidence in support of the content.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=DOC,RSON,PREV, DRIV, USE, COMP] {successor would be PREV w/ inversionInd=true; No support for citation}</t>
@@ -1030,10 +1033,10 @@
 </t>
   </si>
   <si>
-    <t>Logic used by the activity definition</t>
-  </si>
-  <si>
-    <t>A reference to a Library resource containing any formal logic used by the activity definition.</t>
+    <t>アクティビティ定義で使用されるロジック / Logic used by the activity definition</t>
+  </si>
+  <si>
+    <t>アクティビティ定義で使用される正式なロジックを含むライブラリリソースへの参照。 / A reference to a Library resource containing any formal logic used by the activity definition.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=USE].target[classCode=GROUPER,moodCode=EVN]</t>
@@ -1042,16 +1045,16 @@
     <t>ActivityDefinition.kind</t>
   </si>
   <si>
-    <t>Kind of resource</t>
-  </si>
-  <si>
-    <t>A description of the kind of resource the activity definition is representing. For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest. Typically, but not always, this is a Request resource.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
-  </si>
-  <si>
-    <t>The kind of activity the definition is describing.</t>
+    <t>一種のリソース / Kind of resource</t>
+  </si>
+  <si>
+    <t>アクティビティ定義が表しているリソースの種類の説明。たとえば、薬物療法、サービスレクエスト、またはCommunicationRequest。通常、常にではありませんが、これはリクエストリソースです。 / A description of the kind of resource the activity definition is representing. For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest. Typically, but not always, this is a Request resource.</t>
+  </si>
+  <si>
+    <t>どのタイプの拡張機能が許可されているかを決定できます。 / May determine what types of extensions are permitted.</t>
+  </si>
+  <si>
+    <t>定義が説明している種類のアクティビティ。 / The kind of activity the definition is describing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.3.0</t>
@@ -1067,13 +1070,13 @@
 </t>
   </si>
   <si>
-    <t>What profile the resource needs to conform to</t>
-  </si>
-  <si>
-    <t>A profile to which the target of the activity definition is expected to conform.</t>
-  </si>
-  <si>
-    <t>Allows profiles to be used to describe the types of activities that can be performed within a workflow, protocol, or order set.</t>
+    <t>リソースが適合する必要があるプロファイル / What profile the resource needs to conform to</t>
+  </si>
+  <si>
+    <t>アクティビティ定義のターゲットが適合すると予想されるプロファイル。 / A profile to which the target of the activity definition is expected to conform.</t>
+  </si>
+  <si>
+    <t>プロファイルを使用して、ワークフロー、プロトコル、または注文セット内で実行できるアクティビティの種類を説明できます。 / Allows profiles to be used to describe the types of activities that can be performed within a workflow, protocol, or order set.</t>
   </si>
   <si>
     <t>.templateId</t>
@@ -1082,19 +1085,19 @@
     <t>ActivityDefinition.code</t>
   </si>
   <si>
-    <t>Detail type of activity</t>
-  </si>
-  <si>
-    <t>Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
-  </si>
-  <si>
-    <t>Tends to be less relevant for activities involving particular products.</t>
-  </si>
-  <si>
-    <t>Allows matching performed to planned as well as validation against protocols.</t>
-  </si>
-  <si>
-    <t>Detailed type of the activity; e.g. CBC.</t>
+    <t>アクティビティの詳細 / Detail type of activity</t>
+  </si>
+  <si>
+    <t>アクティビティのタイプの詳細な説明。例えばどのラボテスト、どのようなプロシジャー（処置等）、どのようなEncounterがありますか。 / Detailed description of the type of activity; e.g. What lab test, what procedure, what kind of encounter.</t>
+  </si>
+  <si>
+    <t>特定の製品が関与する活動にはあまり関連性がない傾向があります。 / Tends to be less relevant for activities involving particular products.</t>
+  </si>
+  <si>
+    <t>プロトコルに対する検証と同様に、実行されたパフォーマンスを計画することを可能にします。 / Allows matching performed to planned as well as validation against protocols.</t>
+  </si>
+  <si>
+    <t>アクティビティの詳細なタイプ。例えばCBC。 / Detailed type of the activity; e.g. CBC.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code|4.3.0</t>
@@ -1106,13 +1109,13 @@
     <t>ActivityDefinition.intent</t>
   </si>
   <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
-  </si>
-  <si>
-    <t>Indicates the level of authority/intentionality associated with the activity and where the request should fit into the workflow chain.</t>
-  </si>
-  <si>
-    <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
+    <t>提案|計画|指令|注文|オリジナルオーダー|反射順|フィラーオーダー|インスタンスオーダー|オプション / proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+  </si>
+  <si>
+    <t>アクティビティに関連する権限/意図性のレベルと、リクエストがワークフローチェーンに適合する場所を示します。 / Indicates the level of authority/intentionality associated with the activity and where the request should fit into the workflow chain.</t>
+  </si>
+  <si>
+    <t>要求に関連する権限/意図性の程度を示すコード。 / Codes indicating the degree of authority/intentionality associated with a request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.3.0</t>
@@ -1124,13 +1127,13 @@
     <t>ActivityDefinition.priority</t>
   </si>
   <si>
-    <t>routine | urgent | asap | stat</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the activity  should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+    <t>ルーチン|緊急|できるだけ早く|統計 / routine | urgent | asap | stat</t>
+  </si>
+  <si>
+    <t>他のリクエストに関してアクティビティがどれだけ速く対処されるべきかを示します。 / Indicates how quickly the activity  should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
@@ -1142,13 +1145,13 @@
     <t>ActivityDefinition.doNotPerform</t>
   </si>
   <si>
-    <t>True if the activity should not be performed</t>
-  </si>
-  <si>
-    <t>Set this to true if the definition is to indicate that a particular activity should NOT be performed. If true, this element should be interpreted to reinforce a negative coding. For example NPO as a code with a doNotPerform of true would still indicate to NOT perform the action.</t>
-  </si>
-  <si>
-    <t>This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestGroup.</t>
+    <t>アクティビティを実行しないでください / True if the activity should not be performed</t>
+  </si>
+  <si>
+    <t>定義が特定のアクティビティを実行しないでください。真実の場合、この要素はネガティブコーディングを強化するために解釈する必要があります。たとえば、trueのdonotperformを持つコードとしてのNPOは、アクションを実行しないことを示しています。 / Set this to true if the definition is to indicate that a particular activity should NOT be performed. If true, this element should be interpreted to reinforce a negative coding. For example NPO as a code with a doNotPerform of true would still indicate to NOT perform the action.</t>
+  </si>
+  <si>
+    <t>この要素は、進行中の注文をキャンセルするための意思決定サポート応答を伝えるために使用することを意図していません。これは、PlandefinitionまたはRequestGroupの「削除」タイプで行う必要があります。 / This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestGroup.</t>
   </si>
   <si>
     <t>.negationInd { of the realized activity }</t>
@@ -1161,13 +1164,13 @@
 dateTimeAgePeriodRangeDuration</t>
   </si>
   <si>
-    <t>When activity is to occur</t>
-  </si>
-  <si>
-    <t>The period, timing or frequency upon which the described activity is to occur.</t>
-  </si>
-  <si>
-    <t>Allows prompting for activities and detection of missed planned activities.</t>
+    <t>アクティビティが発生する場合 / When activity is to occur</t>
+  </si>
+  <si>
+    <t>記述されたアクティビティが発生する期間、タイミング、または頻度。 / The period, timing or frequency upon which the described activity is to occur.</t>
+  </si>
+  <si>
+    <t>逃した計画されたアクティビティの活動と検出を促すことができます。 / Allows prompting for activities and detection of missed planned activities.</t>
   </si>
   <si>
     <t>.effectiveTime</t>
@@ -1184,16 +1187,16 @@
 </t>
   </si>
   <si>
-    <t>Where it should happen</t>
-  </si>
-  <si>
-    <t>Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
-  </si>
-  <si>
-    <t>May reference a specific clinical location or may just identify a type of location.</t>
-  </si>
-  <si>
-    <t>Helps in planning of activity.</t>
+    <t>それが起こるべき場所 / Where it should happen</t>
+  </si>
+  <si>
+    <t>アクティビティが発生する施設を特定します。例えば自宅、病院、特定の診療所など。 / Identifies the facility where the activity will occur; e.g. home, hospital, specific clinic, etc.</t>
+  </si>
+  <si>
+    <t>特定の臨床的位置を参照するか、場所のタイプを特定する場合があります。 / May reference a specific clinical location or may just identify a type of location.</t>
+  </si>
+  <si>
+    <t>活動の計画に役立ちます。 / Helps in planning of activity.</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role</t>
@@ -1206,13 +1209,13 @@
 </t>
   </si>
   <si>
-    <t>Who should participate in the action</t>
-  </si>
-  <si>
-    <t>Indicates who should participate in performing the action described.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>誰がアクションに参加すべきか / Who should participate in the action</t>
+  </si>
+  <si>
+    <t>説明されているアクションの実行に誰が参加すべきかを示します。 / Indicates who should participate in performing the action described.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1222,10 +1225,10 @@
     <t>ActivityDefinition.participant.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -1237,7 +1240,7 @@
     <t>ActivityDefinition.participant.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -1250,10 +1253,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1263,13 +1267,13 @@
     <t>ActivityDefinition.participant.type</t>
   </si>
   <si>
-    <t>patient | practitioner | related-person | device</t>
-  </si>
-  <si>
-    <t>The type of participant in the action.</t>
-  </si>
-  <si>
-    <t>The type of participant in the activity.</t>
+    <t>患者|開業医|関連者|デバイス / patient | practitioner | related-person | device</t>
+  </si>
+  <si>
+    <t>アクションの参加者のタイプ。 / The type of participant in the action.</t>
+  </si>
+  <si>
+    <t>アクティビティへの参加者のタイプ。 / The type of participant in the activity.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.3.0</t>
@@ -1281,13 +1285,13 @@
     <t>ActivityDefinition.participant.role</t>
   </si>
   <si>
-    <t>E.g. Nurse, Surgeon, Parent, etc.</t>
-  </si>
-  <si>
-    <t>The role the participant should play in performing the described action.</t>
-  </si>
-  <si>
-    <t>Defines roles played by participants for the action.</t>
+    <t>例えば。看護師、外科医、親など / E.g. Nurse, Surgeon, Parent, etc.</t>
+  </si>
+  <si>
+    <t>参加者が説明されたアクションを実行する際に果たすべき役割。 / The role the participant should play in performing the described action.</t>
+  </si>
+  <si>
+    <t>アクションのために参加者が演じる役割を定義します。 / Defines roles played by participants for the action.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
@@ -1299,10 +1303,10 @@
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>What's administered/supplied</t>
-  </si>
-  <si>
-    <t>Identifies the food, drug or other product being consumed or supplied in the activity.</t>
+    <t>管理/提供されているもの / What's administered/supplied</t>
+  </si>
+  <si>
+    <t>活動で消費または供給されている食品、薬物、またはその他の製品を特定します。 / Identifies the food, drug or other product being consumed or supplied in the activity.</t>
   </si>
   <si>
     <t>医薬品コード</t>
@@ -1325,10 +1329,10 @@
 </t>
   </si>
   <si>
-    <t>How much is administered/consumed/supplied</t>
-  </si>
-  <si>
-    <t>Identifies the quantity expected to be consumed at once (per dose, per meal, etc.).</t>
+    <t>投与/消費/供給される金額 / How much is administered/consumed/supplied</t>
+  </si>
+  <si>
+    <t>一度に消費されると予想される量（用量あたり、食事あたりなど）を識別します。 / Identifies the quantity expected to be consumed at once (per dose, per meal, etc.).</t>
   </si>
   <si>
     <t>.quantity {for classCode=SPLY}</t>
@@ -1341,13 +1345,13 @@
 </t>
   </si>
   <si>
-    <t>Detailed dosage instructions</t>
-  </si>
-  <si>
-    <t>Provides detailed dosage instructions in the same way that they are described for MedicationRequest resources.</t>
-  </si>
-  <si>
-    <t>If a dosage instruction is used, the definition should not specify timing or quantity.</t>
+    <t>詳細な用量の指示 / Detailed dosage instructions</t>
+  </si>
+  <si>
+    <t>薬剤リソースのリソースについて説明されているのと同じ方法で、詳細な用量の指示を提供します。 / Provides detailed dosage instructions in the same way that they are described for MedicationRequest resources.</t>
+  </si>
+  <si>
+    <t>投与命令が使用されている場合、定義はタイミングや数量を指定してはなりません。 / If a dosage instruction is used, the definition should not specify timing or quantity.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM; moodCode=DEFN]</t>
@@ -1356,19 +1360,19 @@
     <t>ActivityDefinition.bodySite</t>
   </si>
   <si>
-    <t>What part of body to perform on</t>
-  </si>
-  <si>
-    <t>Indicates the sites on the subject's body where the procedure should be performed (I.e. the target sites).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.type.</t>
-  </si>
-  <si>
-    <t>Knowing where the procedure is made is important for tracking if multiple sites are possible.</t>
-  </si>
-  <si>
-    <t>A code that identifies the anatomical location.</t>
+    <t>パフォーマンスを発揮する身体のどの部分 / What part of body to perform on</t>
+  </si>
+  <si>
+    <t>プロシジャー（処置等）を実行する必要がある被験者の本体のサイト（つまり、ターゲットサイト）を示します。 / Indicates the sites on the subject's body where the procedure should be performed (I.e. the target sites).</t>
+  </si>
+  <si>
+    <t>Servicerequest.Typeで見つかったコードで暗黙的ではない場合にのみ使用されます。 / Only used if not implicit in the code found in ServiceRequest.type.</t>
+  </si>
+  <si>
+    <t>複数のサイトが可能かどうかを追跡するには、プロシジャー（処置等）がどこで行われているかを知ることが重要です。 / Knowing where the procedure is made is important for tracking if multiple sites are possible.</t>
+  </si>
+  <si>
+    <t>解剖学的場所を識別するコード。 / A code that identifies the anatomical location.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -1384,13 +1388,13 @@
 </t>
   </si>
   <si>
-    <t>What specimens are required to perform this action</t>
-  </si>
-  <si>
-    <t>Defines specimen requirements for the action to be performed, such as required specimens for a lab test.</t>
-  </si>
-  <si>
-    <t>Needed to represent lab order definitions.</t>
+    <t>このアクションを実行するために必要な標本 / What specimens are required to perform this action</t>
+  </si>
+  <si>
+    <t>ラボテストに必要な標本など、実行されるアクションの標本要件を定義します。 / Defines specimen requirements for the action to be performed, such as required specimens for a lab test.</t>
+  </si>
+  <si>
+    <t>ラボの順序定義を表すために必要です。 / Needed to represent lab order definitions.</t>
   </si>
   <si>
     <t>ActivityDefinition.observationRequirement</t>
@@ -1400,22 +1404,22 @@
 </t>
   </si>
   <si>
-    <t>What observations are required to perform this action</t>
-  </si>
-  <si>
-    <t>Defines observation requirements for the action to be performed, such as body weight or surface area.</t>
-  </si>
-  <si>
-    <t>Needed to represent observation definitions.</t>
+    <t>このアクションを実行するために必要な観察結果 / What observations are required to perform this action</t>
+  </si>
+  <si>
+    <t>体重や表面積など、実行されるアクションの観測要件を定義します。 / Defines observation requirements for the action to be performed, such as body weight or surface area.</t>
+  </si>
+  <si>
+    <t>観察定義を表すために必要です。 / Needed to represent observation definitions.</t>
   </si>
   <si>
     <t>ActivityDefinition.observationResultRequirement</t>
   </si>
   <si>
-    <t>What observations must be produced by this action</t>
-  </si>
-  <si>
-    <t>Defines the observations that are expected to be produced by the action.</t>
+    <t>このアクションによってどのような観察が生み出されなければなりませんか / What observations must be produced by this action</t>
+  </si>
+  <si>
+    <t>アクションによって生成されると予想される観察結果を定義します。 / Defines the observations that are expected to be produced by the action.</t>
   </si>
   <si>
     <t>ActivityDefinition.transform</t>
@@ -1425,25 +1429,25 @@
 </t>
   </si>
   <si>
-    <t>Transform to apply the template</t>
-  </si>
-  <si>
-    <t>A reference to a StructureMap resource that defines a transform that can be executed to produce the intent resource using the ActivityDefinition instance as the input.</t>
-  </si>
-  <si>
-    <t>Note that if both a transform and dynamic values are specified, the dynamic values will be applied to the result of the transform.</t>
+    <t>テンプレートを適用するために変換します / Transform to apply the template</t>
+  </si>
+  <si>
+    <t>Activitydefinitionインスタンスを入力として使用して、意図リソースを生成するために実行できる変換を定義するStructureMapリソースへの参照。 / A reference to a StructureMap resource that defines a transform that can be executed to produce the intent resource using the ActivityDefinition instance as the input.</t>
+  </si>
+  <si>
+    <t>変換値と動的値の両方が指定されている場合、変換の結果に動的値が適用されることに注意してください。 / Note that if both a transform and dynamic values are specified, the dynamic values will be applied to the result of the transform.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue</t>
   </si>
   <si>
-    <t>Dynamic aspects of the definition</t>
-  </si>
-  <si>
-    <t>Dynamic values that will be evaluated to produce values for elements of the resulting resource. For example, if the dosage of a medication must be computed based on the patient's weight, a dynamic value would be used to specify an expression that calculated the weight, and the path on the request resource that would contain the result.</t>
-  </si>
-  <si>
-    <t>Dynamic values are applied in the order in which they are defined in the ActivityDefinition. Note that if both a transform and dynamic values are specified, the dynamic values will be applied to the result of the transform.</t>
+    <t>定義の動的な側面 / Dynamic aspects of the definition</t>
+  </si>
+  <si>
+    <t>結果のリソースの要素の値を生成するために評価される動的値。たとえば、薬物の投与量を患者の体重に基づいて計算する必要がある場合、動的値を使用して、重量を計算する式と、結果を含むリクエストリソースのパスを指定します。 / Dynamic values that will be evaluated to produce values for elements of the resulting resource. For example, if the dosage of a medication must be computed based on the patient's weight, a dynamic value would be used to specify an expression that calculated the weight, and the path on the request resource that would contain the result.</t>
+  </si>
+  <si>
+    <t>動的値は、Activity -Definitionで定義されている順序で適用されます。変換値と動的値の両方が指定されている場合、変換の結果に動的値が適用されることに注意してください。 / Dynamic values are applied in the order in which they are defined in the ActivityDefinition. Note that if both a transform and dynamic values are specified, the dynamic values will be applied to the result of the transform.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue.id</t>
@@ -1458,13 +1462,13 @@
     <t>ActivityDefinition.dynamicValue.path</t>
   </si>
   <si>
-    <t>The path to the element to be set dynamically</t>
-  </si>
-  <si>
-    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
-  </si>
-  <si>
-    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
+    <t>動的に設定する要素へのパス / The path to the element to be set dynamically</t>
+  </si>
+  <si>
+    <t>カスタマイズされる要素へのパス。これは、式によって定義された計算の結果を保持するリソースのパスです。指定されたパスは、指定されたターゲットタイプのActivity -Definitionで解決可能なFHIRPATHであり、identifier、一定のインデクサー、および関数の制限付きサブセットのみで構成されます。パスは、サブエレメントを通過する予選（。）を含むことができます。また、インデクサー（[x]）が複数のカードサブエレメントを通過します（[simple fhirpathプロファイル]（fhirpath.html＃simpleを参照）。詳細）。 / The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4B/fhirpath.html#simple) for full details).</t>
+  </si>
+  <si>
+    <t>パス属性には、[simple fhirpath Subset]（fhirpath.html＃simple）が含まれています。 / The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4B/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue.expression</t>
@@ -1474,13 +1478,13 @@
 </t>
   </si>
   <si>
-    <t>An expression that provides the dynamic value for the customization</t>
-  </si>
-  <si>
-    <t>An expression specifying the value of the customized element.</t>
-  </si>
-  <si>
-    <t>The expression may be inlined, or may be a reference to a named expression within a logic library referenced by the library element.</t>
+    <t>カスタマイズの動的値を提供する式 / An expression that provides the dynamic value for the customization</t>
+  </si>
+  <si>
+    <t>カスタマイズされた要素の値を指定する式。 / An expression specifying the value of the customized element.</t>
+  </si>
+  <si>
+    <t>式にインラキングされる場合があるか、ライブラリ要素によって参照されるロジックライブラリ内の名前付き式への参照である場合があります。 / The expression may be inlined, or may be a reference to a named expression within a logic library referenced by the library element.</t>
   </si>
 </sst>
 </file>
@@ -1811,7 +1815,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="118.390625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.82421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
